--- a/Audit_Code/public/SOC2_Type2_Modified.xlsx
+++ b/Audit_Code/public/SOC2_Type2_Modified.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Compliance\Audit_Code\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammad.abdullah\Documents\Compliance\Audit_Code\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15348" windowHeight="4632"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$F$94</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -709,7 +709,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -1134,18 +1134,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F94"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.125" style="9"/>
-    <col min="2" max="2" width="8.875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="29.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="37.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="107.125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.125" style="2"/>
+    <col min="1" max="1" width="9.09765625" style="9"/>
+    <col min="2" max="2" width="8.8984375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="29.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="37.09765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="107.09765625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.09765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="3" t="s">
@@ -1199,7 +1199,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.5">
+    <row r="4" spans="1:6" ht="27.6">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="28.5">
+    <row r="8" spans="1:6" ht="27.6">
       <c r="A8" s="8">
         <v>2</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="42.75">
+    <row r="10" spans="1:6" ht="41.4">
       <c r="A10" s="8">
         <v>2</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="28.5">
+    <row r="11" spans="1:6" ht="27.6">
       <c r="A11" s="8">
         <v>2</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="42.75">
+    <row r="12" spans="1:6" ht="41.4">
       <c r="A12" s="8">
         <v>3</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.5">
+    <row r="13" spans="1:6" ht="27.6">
       <c r="A13" s="8">
         <v>3</v>
       </c>
@@ -1404,14 +1404,12 @@
         <v>3</v>
       </c>
       <c r="B14" s="8">
-        <f t="shared" ref="B14:B35" si="0">B13+0.1</f>
-        <v>3.3000000000000003</v>
+        <v>3.3</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" ref="D14:D67" si="1">D13+1</f>
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1426,14 +1424,12 @@
         <v>3</v>
       </c>
       <c r="B15" s="8">
-        <f t="shared" si="0"/>
-        <v>3.4000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -1443,19 +1439,17 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="28.5">
+    <row r="16" spans="1:6" ht="27.6">
       <c r="A16" s="8">
         <v>3</v>
       </c>
       <c r="B16" s="8">
-        <f t="shared" si="0"/>
-        <v>3.5000000000000004</v>
+        <v>3.5</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -1465,19 +1459,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="42.75">
+    <row r="17" spans="1:6" ht="41.4">
       <c r="A17" s="8">
         <v>3</v>
       </c>
       <c r="B17" s="8">
-        <f t="shared" si="0"/>
-        <v>3.6000000000000005</v>
+        <v>3.6</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D17" s="8">
-        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E17" s="4" t="s">
@@ -1498,7 +1490,6 @@
         <v>18</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -1508,19 +1499,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="28.5">
+    <row r="19" spans="1:6" ht="27.6">
       <c r="A19" s="8">
         <v>4</v>
       </c>
       <c r="B19" s="8">
-        <f t="shared" si="0"/>
-        <v>4.1999999999999993</v>
+        <v>4.2</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="8">
-        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -1530,19 +1519,17 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="28.5">
+    <row r="20" spans="1:6" ht="27.6">
       <c r="A20" s="8">
         <v>4</v>
       </c>
       <c r="B20" s="8">
-        <f t="shared" si="0"/>
-        <v>4.2999999999999989</v>
+        <v>4.3</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -1552,19 +1539,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="42.75">
+    <row r="21" spans="1:6" ht="41.4">
       <c r="A21" s="8">
         <v>4</v>
       </c>
       <c r="B21" s="8">
-        <f t="shared" si="0"/>
-        <v>4.3999999999999986</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="8">
-        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
@@ -1574,19 +1559,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="28.5">
+    <row r="22" spans="1:6" ht="27.6">
       <c r="A22" s="8">
         <v>4</v>
       </c>
       <c r="B22" s="8">
-        <f t="shared" si="0"/>
-        <v>4.4999999999999982</v>
+        <v>4.5</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -1596,19 +1579,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="28.5">
+    <row r="23" spans="1:6" ht="27.6">
       <c r="A23" s="8">
         <v>4</v>
       </c>
       <c r="B23" s="8">
-        <f t="shared" si="0"/>
-        <v>4.5999999999999979</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="E23" s="4" t="s">
@@ -1618,19 +1599,17 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="42.75">
+    <row r="24" spans="1:6" ht="41.4">
       <c r="A24" s="8">
         <v>4</v>
       </c>
       <c r="B24" s="8">
-        <f t="shared" si="0"/>
-        <v>4.6999999999999975</v>
+        <v>4.7</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="8">
-        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="E24" s="4" t="s">
@@ -1640,19 +1619,17 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="28.5">
+    <row r="25" spans="1:6" ht="27.6">
       <c r="A25" s="8">
         <v>4</v>
       </c>
       <c r="B25" s="8">
-        <f t="shared" si="0"/>
-        <v>4.7999999999999972</v>
+        <v>4.8</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="E25" s="4" t="s">
@@ -1662,7 +1639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="28.5">
+    <row r="26" spans="1:6" ht="27.6">
       <c r="A26" s="8">
         <v>5</v>
       </c>
@@ -1673,7 +1650,6 @@
         <v>5</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -1683,19 +1659,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="28.5">
+    <row r="27" spans="1:6" ht="27.6">
       <c r="A27" s="8">
         <v>5</v>
       </c>
       <c r="B27" s="8">
-        <f t="shared" si="0"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
@@ -1705,19 +1679,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="42.75">
+    <row r="28" spans="1:6" ht="41.4">
       <c r="A28" s="8">
         <v>5</v>
       </c>
       <c r="B28" s="8">
-        <f t="shared" si="0"/>
-        <v>5.1999999999999993</v>
+        <v>5.2</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="E28" s="4" t="s">
@@ -1727,19 +1699,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="28.5">
+    <row r="29" spans="1:6" ht="27.6">
       <c r="A29" s="8">
         <v>5</v>
       </c>
       <c r="B29" s="8">
-        <f t="shared" si="0"/>
-        <v>5.2999999999999989</v>
+        <v>5.3</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="E29" s="4" t="s">
@@ -1749,19 +1719,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="42.75">
+    <row r="30" spans="1:6" ht="27.6">
       <c r="A30" s="8">
         <v>5</v>
       </c>
       <c r="B30" s="8">
-        <f t="shared" si="0"/>
-        <v>5.3999999999999986</v>
+        <v>5.4</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="8">
-        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="E30" s="4" t="s">
@@ -1776,14 +1744,12 @@
         <v>5</v>
       </c>
       <c r="B31" s="8">
-        <f t="shared" si="0"/>
-        <v>5.4999999999999982</v>
+        <v>5.5</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="E31" s="4" t="s">
@@ -1793,19 +1759,17 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.5">
+    <row r="32" spans="1:6" ht="27.6">
       <c r="A32" s="8">
         <v>5</v>
       </c>
       <c r="B32" s="8">
-        <f t="shared" si="0"/>
-        <v>5.5999999999999979</v>
+        <v>5.6</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="E32" s="4" t="s">
@@ -1820,14 +1784,12 @@
         <v>5</v>
       </c>
       <c r="B33" s="8">
-        <f t="shared" si="0"/>
-        <v>5.6999999999999975</v>
+        <v>5.7</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D33" s="8">
-        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="E33" s="4" t="s">
@@ -1837,19 +1799,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="28.5">
+    <row r="34" spans="1:6" ht="27.6">
       <c r="A34" s="8">
         <v>5</v>
       </c>
       <c r="B34" s="8">
-        <f t="shared" si="0"/>
-        <v>5.7999999999999972</v>
+        <v>5.8</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -1864,14 +1824,12 @@
         <v>5</v>
       </c>
       <c r="B35" s="8">
-        <f t="shared" si="0"/>
-        <v>5.8999999999999968</v>
+        <v>5.9</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="8">
-        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="E35" s="4" t="s">
@@ -1892,7 +1850,6 @@
         <v>93</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="E36" s="4" t="s">
@@ -1907,14 +1864,12 @@
         <v>7</v>
       </c>
       <c r="B37" s="8">
-        <f t="shared" ref="B37:B53" si="2">B36+1</f>
         <v>7.1</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="E37" s="4" t="s">
@@ -1924,7 +1879,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="28.5">
+    <row r="38" spans="1:6" ht="27.6">
       <c r="A38" s="8">
         <v>8</v>
       </c>
@@ -1935,7 +1890,6 @@
         <v>90</v>
       </c>
       <c r="D38" s="8">
-        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="E38" s="4" t="s">
@@ -1945,19 +1899,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="28.5">
+    <row r="39" spans="1:6" ht="27.6">
       <c r="A39" s="8">
         <v>8</v>
       </c>
       <c r="B39" s="8">
-        <f t="shared" ref="B39:B45" si="3">B38+0.1</f>
         <v>8.1999999999999993</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="E39" s="4" t="s">
@@ -1967,19 +1919,17 @@
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="28.5">
+    <row r="40" spans="1:6" ht="27.6">
       <c r="A40" s="8">
         <v>8</v>
       </c>
       <c r="B40" s="8">
-        <f t="shared" si="3"/>
-        <v>8.2999999999999989</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D40" s="8">
-        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="E40" s="4" t="s">
@@ -1989,19 +1939,17 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="28.5">
+    <row r="41" spans="1:6" ht="27.6">
       <c r="A41" s="8">
         <v>8</v>
       </c>
       <c r="B41" s="8">
-        <f t="shared" si="3"/>
-        <v>8.3999999999999986</v>
+        <v>8.4</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D41" s="8">
-        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="E41" s="4" t="s">
@@ -2011,19 +1959,17 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="28.5">
+    <row r="42" spans="1:6" ht="27.6">
       <c r="A42" s="8">
         <v>8</v>
       </c>
       <c r="B42" s="8">
-        <f t="shared" si="3"/>
-        <v>8.4999999999999982</v>
+        <v>8.5</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D42" s="8">
-        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="E42" s="4" t="s">
@@ -2033,19 +1979,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="28.5">
+    <row r="43" spans="1:6" ht="27.6">
       <c r="A43" s="8">
         <v>8</v>
       </c>
       <c r="B43" s="8">
-        <f t="shared" si="3"/>
-        <v>8.5999999999999979</v>
+        <v>8.6</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D43" s="8">
-        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="E43" s="4" t="s">
@@ -2055,19 +1999,17 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="28.5">
+    <row r="44" spans="1:6" ht="27.6">
       <c r="A44" s="8">
         <v>8</v>
       </c>
       <c r="B44" s="8">
-        <f t="shared" si="3"/>
-        <v>8.6999999999999975</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="8">
-        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="E44" s="4" t="s">
@@ -2077,19 +2019,17 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="28.5">
+    <row r="45" spans="1:6" ht="27.6">
       <c r="A45" s="8">
         <v>8</v>
       </c>
       <c r="B45" s="8">
-        <f t="shared" si="3"/>
-        <v>8.7999999999999972</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D45" s="8">
-        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="E45" s="4" t="s">
@@ -2099,19 +2039,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="28.5">
+    <row r="46" spans="1:6" ht="27.6">
       <c r="A46" s="8">
         <v>8</v>
       </c>
       <c r="B46" s="8">
-        <f>B45+0.1</f>
-        <v>8.8999999999999968</v>
+        <v>8.9</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>83</v>
       </c>
       <c r="D46" s="8">
-        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="E46" s="4" t="s">
@@ -2121,7 +2059,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="28.5">
+    <row r="47" spans="1:6" ht="27.6">
       <c r="A47" s="8">
         <v>8</v>
       </c>
@@ -2132,7 +2070,6 @@
         <v>90</v>
       </c>
       <c r="D47" s="8">
-        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="E47" s="4" t="s">
@@ -2142,7 +2079,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="28.5">
+    <row r="48" spans="1:6" ht="27.6">
       <c r="A48" s="8">
         <v>8</v>
       </c>
@@ -2153,7 +2090,6 @@
         <v>90</v>
       </c>
       <c r="D48" s="8">
-        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="E48" s="4" t="s">
@@ -2163,7 +2099,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="28.5">
+    <row r="49" spans="1:6" ht="27.6">
       <c r="A49" s="8">
         <v>9</v>
       </c>
@@ -2174,7 +2110,6 @@
         <v>99</v>
       </c>
       <c r="D49" s="8">
-        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="E49" s="4" t="s">
@@ -2184,19 +2119,17 @@
         <v>171</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="28.5">
+    <row r="50" spans="1:6" ht="27.6">
       <c r="A50" s="8">
         <v>10</v>
       </c>
       <c r="B50" s="8">
-        <f t="shared" si="2"/>
         <v>10.1</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>104</v>
       </c>
       <c r="D50" s="8">
-        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="E50" s="4" t="s">
@@ -2206,19 +2139,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="28.5">
+    <row r="51" spans="1:6" ht="27.6">
       <c r="A51" s="8">
         <v>11</v>
       </c>
       <c r="B51" s="8">
-        <f t="shared" si="2"/>
         <v>11.1</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>105</v>
       </c>
       <c r="D51" s="8">
-        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="E51" s="4" t="s">
@@ -2228,19 +2159,17 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="28.5">
+    <row r="52" spans="1:6" ht="27.6">
       <c r="A52" s="8">
         <v>12</v>
       </c>
       <c r="B52" s="8">
-        <f t="shared" si="2"/>
         <v>12.1</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>95</v>
       </c>
       <c r="D52" s="8">
-        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -2250,19 +2179,17 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="42.75">
+    <row r="53" spans="1:6" ht="41.4">
       <c r="A53" s="8">
         <v>13</v>
       </c>
       <c r="B53" s="8">
-        <f t="shared" si="2"/>
         <v>13.1</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>106</v>
       </c>
       <c r="D53" s="8">
-        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="E53" s="4" t="s">
@@ -2272,7 +2199,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="42.75">
+    <row r="54" spans="1:6" ht="41.4">
       <c r="A54" s="8">
         <v>14</v>
       </c>
@@ -2283,7 +2210,6 @@
         <v>28</v>
       </c>
       <c r="D54" s="8">
-        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="E54" s="4" t="s">
@@ -2293,19 +2219,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="28.5">
+    <row r="55" spans="1:6" ht="27.6">
       <c r="A55" s="8">
         <v>14</v>
       </c>
       <c r="B55" s="8">
-        <f t="shared" ref="B55:B62" si="4">B54+0.1</f>
         <v>14.2</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="8">
-        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="E55" s="4" t="s">
@@ -2315,19 +2239,17 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="28.5">
+    <row r="56" spans="1:6" ht="27.6">
       <c r="A56" s="8">
         <v>14</v>
       </c>
       <c r="B56" s="8">
-        <f t="shared" si="4"/>
-        <v>14.299999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="8">
-        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="E56" s="4" t="s">
@@ -2337,19 +2259,17 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="28.5">
+    <row r="57" spans="1:6" ht="27.6">
       <c r="A57" s="8">
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <f t="shared" si="4"/>
-        <v>14.399999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="8">
-        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="E57" s="4" t="s">
@@ -2359,19 +2279,17 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="28.5">
+    <row r="58" spans="1:6" ht="27.6">
       <c r="A58" s="8">
         <v>14</v>
       </c>
       <c r="B58" s="8">
-        <f t="shared" si="4"/>
-        <v>14.499999999999998</v>
+        <v>14.5</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="E58" s="4" t="s">
@@ -2381,19 +2299,17 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="28.5">
+    <row r="59" spans="1:6" ht="27.6">
       <c r="A59" s="8">
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <f t="shared" si="4"/>
-        <v>14.599999999999998</v>
+        <v>14.6</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="8">
-        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="E59" s="4" t="s">
@@ -2403,19 +2319,17 @@
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="42.75">
+    <row r="60" spans="1:6" ht="41.4">
       <c r="A60" s="8">
         <v>14</v>
       </c>
       <c r="B60" s="8">
-        <f t="shared" si="4"/>
-        <v>14.699999999999998</v>
+        <v>14.7</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D60" s="8">
-        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="E60" s="4" t="s">
@@ -2425,19 +2339,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="28.5">
+    <row r="61" spans="1:6" ht="27.6">
       <c r="A61" s="8">
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <f t="shared" si="4"/>
-        <v>14.799999999999997</v>
+        <v>14.8</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="8">
-        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="E61" s="4" t="s">
@@ -2447,19 +2359,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="28.5">
+    <row r="62" spans="1:6" ht="27.6">
       <c r="A62" s="8">
         <v>14</v>
       </c>
       <c r="B62" s="8">
-        <f t="shared" si="4"/>
-        <v>14.899999999999997</v>
+        <v>14.9</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="8">
-        <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="E62" s="4" t="s">
@@ -2469,7 +2379,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="57">
+    <row r="63" spans="1:6" ht="55.2">
       <c r="A63" s="8">
         <v>14</v>
       </c>
@@ -2480,7 +2390,6 @@
         <v>28</v>
       </c>
       <c r="D63" s="8">
-        <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="E63" s="4" t="s">
@@ -2490,7 +2399,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="42.75">
+    <row r="64" spans="1:6" ht="41.4">
       <c r="A64" s="8">
         <v>14</v>
       </c>
@@ -2501,7 +2410,6 @@
         <v>28</v>
       </c>
       <c r="D64" s="8">
-        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="E64" s="4" t="s">
@@ -2511,7 +2419,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="28.5">
+    <row r="65" spans="1:6" ht="27.6">
       <c r="A65" s="8">
         <v>14</v>
       </c>
@@ -2522,7 +2430,6 @@
         <v>28</v>
       </c>
       <c r="D65" s="8">
-        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="E65" s="4" t="s">
@@ -2532,7 +2439,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="42.75">
+    <row r="66" spans="1:6" ht="41.4">
       <c r="A66" s="8">
         <v>14</v>
       </c>
@@ -2543,7 +2450,6 @@
         <v>28</v>
       </c>
       <c r="D66" s="8">
-        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="E66" s="4" t="s">
@@ -2553,7 +2459,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="28.5">
+    <row r="67" spans="1:6" ht="27.6">
       <c r="A67" s="8">
         <v>14</v>
       </c>
@@ -2564,7 +2470,6 @@
         <v>28</v>
       </c>
       <c r="D67" s="8">
-        <f t="shared" si="1"/>
         <v>66</v>
       </c>
       <c r="E67" s="4" t="s">
@@ -2574,7 +2479,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="28.5">
+    <row r="68" spans="1:6" ht="27.6">
       <c r="A68" s="8">
         <v>14</v>
       </c>
@@ -2585,7 +2490,6 @@
         <v>28</v>
       </c>
       <c r="D68" s="8">
-        <f t="shared" ref="D68:D94" si="5">D67+1</f>
         <v>67</v>
       </c>
       <c r="E68" s="4" t="s">
@@ -2595,7 +2499,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="28.5">
+    <row r="69" spans="1:6" ht="27.6">
       <c r="A69" s="8">
         <v>14</v>
       </c>
@@ -2606,7 +2510,6 @@
         <v>28</v>
       </c>
       <c r="D69" s="8">
-        <f t="shared" si="5"/>
         <v>68</v>
       </c>
       <c r="E69" s="4" t="s">
@@ -2616,7 +2519,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="42.75">
+    <row r="70" spans="1:6" ht="41.4">
       <c r="A70" s="8">
         <v>14</v>
       </c>
@@ -2627,7 +2530,6 @@
         <v>28</v>
       </c>
       <c r="D70" s="8">
-        <f t="shared" si="5"/>
         <v>69</v>
       </c>
       <c r="E70" s="4" t="s">
@@ -2637,7 +2539,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="42.75">
+    <row r="71" spans="1:6" ht="41.4">
       <c r="A71" s="8">
         <v>15</v>
       </c>
@@ -2648,7 +2550,6 @@
         <v>26</v>
       </c>
       <c r="D71" s="8">
-        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="E71" s="4" t="s">
@@ -2658,7 +2559,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="28.5">
+    <row r="72" spans="1:6" ht="27.6">
       <c r="A72" s="8">
         <v>16</v>
       </c>
@@ -2669,7 +2570,6 @@
         <v>13</v>
       </c>
       <c r="D72" s="8">
-        <f t="shared" si="5"/>
         <v>71</v>
       </c>
       <c r="E72" s="4" t="s">
@@ -2684,14 +2584,12 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <f>B72+0.1</f>
-        <v>16.200000000000003</v>
+        <v>16.2</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D73" s="8">
-        <f t="shared" si="5"/>
         <v>72</v>
       </c>
       <c r="E73" s="4" t="s">
@@ -2706,14 +2604,12 @@
         <v>16</v>
       </c>
       <c r="B74" s="8">
-        <f t="shared" ref="B74:B80" si="6">B73+0.1</f>
-        <v>16.300000000000004</v>
+        <v>16.3</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D74" s="8">
-        <f t="shared" si="5"/>
         <v>73</v>
       </c>
       <c r="E74" s="4" t="s">
@@ -2723,19 +2619,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="28.5">
+    <row r="75" spans="1:6" ht="27.6">
       <c r="A75" s="8">
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <f t="shared" si="6"/>
-        <v>16.400000000000006</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D75" s="8">
-        <f t="shared" si="5"/>
         <v>74</v>
       </c>
       <c r="E75" s="4" t="s">
@@ -2750,14 +2644,12 @@
         <v>16</v>
       </c>
       <c r="B76" s="8">
-        <f t="shared" si="6"/>
-        <v>16.500000000000007</v>
+        <v>16.5</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D76" s="8">
-        <f t="shared" si="5"/>
         <v>75</v>
       </c>
       <c r="E76" s="4" t="s">
@@ -2767,19 +2659,17 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="28.5">
+    <row r="77" spans="1:6" ht="27.6">
       <c r="A77" s="8">
         <v>16</v>
       </c>
       <c r="B77" s="8">
-        <f t="shared" si="6"/>
-        <v>16.600000000000009</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="8">
-        <f t="shared" si="5"/>
         <v>76</v>
       </c>
       <c r="E77" s="4" t="s">
@@ -2789,19 +2679,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="28.5">
+    <row r="78" spans="1:6" ht="27.6">
       <c r="A78" s="8">
         <v>16</v>
       </c>
       <c r="B78" s="8">
-        <f t="shared" si="6"/>
-        <v>16.70000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D78" s="8">
-        <f t="shared" si="5"/>
         <v>77</v>
       </c>
       <c r="E78" s="4" t="s">
@@ -2811,19 +2699,17 @@
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="57">
+    <row r="79" spans="1:6" ht="55.2">
       <c r="A79" s="8">
         <v>16</v>
       </c>
       <c r="B79" s="8">
-        <f t="shared" si="6"/>
-        <v>16.800000000000011</v>
+        <v>16.8</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D79" s="8">
-        <f t="shared" si="5"/>
         <v>78</v>
       </c>
       <c r="E79" s="4" t="s">
@@ -2833,19 +2719,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="42.75">
+    <row r="80" spans="1:6" ht="41.4">
       <c r="A80" s="8">
         <v>16</v>
       </c>
       <c r="B80" s="8">
-        <f t="shared" si="6"/>
-        <v>16.900000000000013</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="8">
-        <f t="shared" si="5"/>
         <v>79</v>
       </c>
       <c r="E80" s="4" t="s">
@@ -2855,7 +2739,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="42.75">
+    <row r="81" spans="1:6" ht="41.4">
       <c r="A81" s="8">
         <v>16</v>
       </c>
@@ -2866,7 +2750,6 @@
         <v>13</v>
       </c>
       <c r="D81" s="8">
-        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="E81" s="4" t="s">
@@ -2876,7 +2759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="42.75">
+    <row r="82" spans="1:6" ht="41.4">
       <c r="A82" s="8">
         <v>16</v>
       </c>
@@ -2887,7 +2770,6 @@
         <v>13</v>
       </c>
       <c r="D82" s="8">
-        <f t="shared" si="5"/>
         <v>81</v>
       </c>
       <c r="E82" s="4" t="s">
@@ -2897,7 +2779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="42.75">
+    <row r="83" spans="1:6" ht="27.6">
       <c r="A83" s="8">
         <v>17</v>
       </c>
@@ -2908,7 +2790,6 @@
         <v>84</v>
       </c>
       <c r="D83" s="8">
-        <f t="shared" si="5"/>
         <v>82</v>
       </c>
       <c r="E83" s="4" t="s">
@@ -2918,19 +2799,17 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="42.75">
+    <row r="84" spans="1:6" ht="27.6">
       <c r="A84" s="8">
         <v>17</v>
       </c>
       <c r="B84" s="8">
-        <f>B83+0.1</f>
-        <v>17.200000000000003</v>
+        <v>17.2</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D84" s="8">
-        <f t="shared" si="5"/>
         <v>83</v>
       </c>
       <c r="E84" s="4" t="s">
@@ -2945,14 +2824,12 @@
         <v>17</v>
       </c>
       <c r="B85" s="8">
-        <f t="shared" ref="B85:B91" si="7">B84+0.1</f>
-        <v>17.300000000000004</v>
+        <v>17.3</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D85" s="8">
-        <f t="shared" si="5"/>
         <v>84</v>
       </c>
       <c r="E85" s="4" t="s">
@@ -2962,19 +2839,17 @@
         <v>209</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="28.5">
+    <row r="86" spans="1:6" ht="27.6">
       <c r="A86" s="8">
         <v>17</v>
       </c>
       <c r="B86" s="8">
-        <f t="shared" si="7"/>
-        <v>17.400000000000006</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D86" s="8">
-        <f t="shared" si="5"/>
         <v>85</v>
       </c>
       <c r="E86" s="4" t="s">
@@ -2989,14 +2864,12 @@
         <v>17</v>
       </c>
       <c r="B87" s="8">
-        <f t="shared" si="7"/>
-        <v>17.500000000000007</v>
+        <v>17.5</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D87" s="8">
-        <f t="shared" si="5"/>
         <v>86</v>
       </c>
       <c r="E87" s="4" t="s">
@@ -3006,19 +2879,17 @@
         <v>212</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="42.75">
+    <row r="88" spans="1:6" ht="41.4">
       <c r="A88" s="8">
         <v>17</v>
       </c>
       <c r="B88" s="8">
-        <f t="shared" si="7"/>
-        <v>17.600000000000009</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D88" s="8">
-        <f t="shared" si="5"/>
         <v>87</v>
       </c>
       <c r="E88" s="4" t="s">
@@ -3028,19 +2899,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="28.5">
+    <row r="89" spans="1:6" ht="27.6">
       <c r="A89" s="8">
         <v>17</v>
       </c>
       <c r="B89" s="8">
-        <f t="shared" si="7"/>
-        <v>17.70000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D89" s="8">
-        <f t="shared" si="5"/>
         <v>88</v>
       </c>
       <c r="E89" s="4" t="s">
@@ -3050,19 +2919,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="28.5">
+    <row r="90" spans="1:6" ht="27.6">
       <c r="A90" s="8">
         <v>17</v>
       </c>
       <c r="B90" s="8">
-        <f t="shared" si="7"/>
-        <v>17.800000000000011</v>
+        <v>17.8</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D90" s="8">
-        <f t="shared" si="5"/>
         <v>89</v>
       </c>
       <c r="E90" s="4" t="s">
@@ -3072,19 +2939,17 @@
         <v>216</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="42.75">
+    <row r="91" spans="1:6" ht="41.4">
       <c r="A91" s="8">
         <v>17</v>
       </c>
       <c r="B91" s="8">
-        <f t="shared" si="7"/>
-        <v>17.900000000000013</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D91" s="8">
-        <f t="shared" si="5"/>
         <v>90</v>
       </c>
       <c r="E91" s="4" t="s">
@@ -3105,7 +2970,6 @@
         <v>84</v>
       </c>
       <c r="D92" s="8">
-        <f t="shared" si="5"/>
         <v>91</v>
       </c>
       <c r="E92" s="4" t="s">
@@ -3115,19 +2979,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="28.5">
+    <row r="93" spans="1:6" ht="27.6">
       <c r="A93" s="8">
         <v>18</v>
       </c>
       <c r="B93" s="8">
-        <f t="shared" ref="B93:B94" si="8">B92+1</f>
         <v>18.100000000000001</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D93" s="8">
-        <f t="shared" si="5"/>
         <v>92</v>
       </c>
       <c r="E93" s="4" t="s">
@@ -3142,14 +3004,12 @@
         <v>19</v>
       </c>
       <c r="B94" s="8">
-        <f t="shared" si="8"/>
         <v>19.100000000000001</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D94" s="8">
-        <f t="shared" si="5"/>
         <v>93</v>
       </c>
       <c r="E94" s="4" t="s">

--- a/Audit_Code/public/SOC2_Type2_Modified.xlsx
+++ b/Audit_Code/public/SOC2_Type2_Modified.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammad.abdullah\Documents\Compliance\Audit_Code\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Compliance\Audit_Code\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15348" windowHeight="4632"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,21 +17,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$F$94</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -361,9 +350,6 @@
     <t>IT Operational Anomalies Reporting</t>
   </si>
   <si>
-    <t>Trust Criteria Domain</t>
-  </si>
-  <si>
     <t>Trust Criteria Principle</t>
   </si>
   <si>
@@ -704,12 +690,15 @@
   </si>
   <si>
     <t>Regular vulnerability scans.</t>
+  </si>
+  <si>
+    <t>Domain</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -1134,26 +1123,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F94"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" style="9"/>
-    <col min="2" max="2" width="8.8984375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="29.59765625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.8984375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="37.09765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="107.09765625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.09765625" style="2"/>
+    <col min="1" max="1" width="9.125" style="9"/>
+    <col min="2" max="2" width="8.875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="29.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="37.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="107.125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="15">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="3" t="s">
-        <v>107</v>
+        <v>221</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>45</v>
@@ -1173,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>97</v>
@@ -1193,13 +1182,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="27.6">
+    <row r="4" spans="1:6" ht="28.5">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -1213,7 +1202,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>0</v>
@@ -1233,7 +1222,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>76</v>
@@ -1253,7 +1242,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>72</v>
@@ -1273,13 +1262,13 @@
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="27.6">
+    <row r="8" spans="1:6" ht="28.5">
       <c r="A8" s="8">
         <v>2</v>
       </c>
@@ -1293,7 +1282,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>71</v>
@@ -1313,13 +1302,13 @@
         <v>8</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="41.4">
+    <row r="10" spans="1:6" ht="42.75">
       <c r="A10" s="8">
         <v>2</v>
       </c>
@@ -1333,13 +1322,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="27.6">
+    <row r="11" spans="1:6" ht="28.5">
       <c r="A11" s="8">
         <v>2</v>
       </c>
@@ -1353,13 +1342,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="41.4">
+    <row r="12" spans="1:6" ht="42.75">
       <c r="A12" s="8">
         <v>3</v>
       </c>
@@ -1373,13 +1362,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="27.6">
+    <row r="13" spans="1:6" ht="28.5">
       <c r="A13" s="8">
         <v>3</v>
       </c>
@@ -1393,7 +1382,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>44</v>
@@ -1413,7 +1402,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>73</v>
@@ -1433,13 +1422,13 @@
         <v>14</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="27.6">
+    <row r="16" spans="1:6" ht="28.5">
       <c r="A16" s="8">
         <v>3</v>
       </c>
@@ -1453,13 +1442,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="41.4">
+    <row r="17" spans="1:6" ht="42.75">
       <c r="A17" s="8">
         <v>3</v>
       </c>
@@ -1473,7 +1462,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>41</v>
@@ -1493,13 +1482,13 @@
         <v>17</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="27.6">
+    <row r="19" spans="1:6" ht="28.5">
       <c r="A19" s="8">
         <v>4</v>
       </c>
@@ -1513,13 +1502,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="27.6">
+    <row r="20" spans="1:6" ht="28.5">
       <c r="A20" s="8">
         <v>4</v>
       </c>
@@ -1533,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="41.4">
+    <row r="21" spans="1:6" ht="42.75">
       <c r="A21" s="8">
         <v>4</v>
       </c>
@@ -1553,13 +1542,13 @@
         <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="27.6">
+    <row r="22" spans="1:6" ht="28.5">
       <c r="A22" s="8">
         <v>4</v>
       </c>
@@ -1573,13 +1562,13 @@
         <v>21</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="27.6">
+    <row r="23" spans="1:6" ht="28.5">
       <c r="A23" s="8">
         <v>4</v>
       </c>
@@ -1593,13 +1582,13 @@
         <v>22</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="41.4">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="42.75">
       <c r="A24" s="8">
         <v>4</v>
       </c>
@@ -1613,13 +1602,13 @@
         <v>23</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="27.6">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28.5">
       <c r="A25" s="8">
         <v>4</v>
       </c>
@@ -1633,13 +1622,13 @@
         <v>24</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="27.6">
+    <row r="26" spans="1:6" ht="28.5">
       <c r="A26" s="8">
         <v>5</v>
       </c>
@@ -1653,13 +1642,13 @@
         <v>25</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="27.6">
+    <row r="27" spans="1:6" ht="28.5">
       <c r="A27" s="8">
         <v>5</v>
       </c>
@@ -1673,13 +1662,13 @@
         <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="41.4">
+    <row r="28" spans="1:6" ht="42.75">
       <c r="A28" s="8">
         <v>5</v>
       </c>
@@ -1693,13 +1682,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="27.6">
+    <row r="29" spans="1:6" ht="28.5">
       <c r="A29" s="8">
         <v>5</v>
       </c>
@@ -1713,13 +1702,13 @@
         <v>28</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="27.6">
+    <row r="30" spans="1:6" ht="42.75">
       <c r="A30" s="8">
         <v>5</v>
       </c>
@@ -1733,7 +1722,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>6</v>
@@ -1753,13 +1742,13 @@
         <v>30</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="27.6">
+    <row r="32" spans="1:6" ht="28.5">
       <c r="A32" s="8">
         <v>5</v>
       </c>
@@ -1773,7 +1762,7 @@
         <v>31</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>87</v>
@@ -1793,13 +1782,13 @@
         <v>32</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="27.6">
+    <row r="34" spans="1:6" ht="28.5">
       <c r="A34" s="8">
         <v>5</v>
       </c>
@@ -1813,7 +1802,7 @@
         <v>33</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>8</v>
@@ -1833,7 +1822,7 @@
         <v>34</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>11</v>
@@ -1853,7 +1842,7 @@
         <v>35</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>79</v>
@@ -1873,13 +1862,13 @@
         <v>36</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="27.6">
+    <row r="38" spans="1:6" ht="28.5">
       <c r="A38" s="8">
         <v>8</v>
       </c>
@@ -1893,13 +1882,13 @@
         <v>37</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="27.6">
+    <row r="39" spans="1:6" ht="28.5">
       <c r="A39" s="8">
         <v>8</v>
       </c>
@@ -1913,13 +1902,13 @@
         <v>38</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="27.6">
+    <row r="40" spans="1:6" ht="28.5">
       <c r="A40" s="8">
         <v>8</v>
       </c>
@@ -1933,13 +1922,13 @@
         <v>39</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="27.6">
+    <row r="41" spans="1:6" ht="28.5">
       <c r="A41" s="8">
         <v>8</v>
       </c>
@@ -1953,13 +1942,13 @@
         <v>40</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="27.6">
+    <row r="42" spans="1:6" ht="28.5">
       <c r="A42" s="8">
         <v>8</v>
       </c>
@@ -1973,13 +1962,13 @@
         <v>41</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="27.6">
+    <row r="43" spans="1:6" ht="28.5">
       <c r="A43" s="8">
         <v>8</v>
       </c>
@@ -1993,13 +1982,13 @@
         <v>42</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="27.6">
+    <row r="44" spans="1:6" ht="28.5">
       <c r="A44" s="8">
         <v>8</v>
       </c>
@@ -2013,13 +2002,13 @@
         <v>43</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="27.6">
+    <row r="45" spans="1:6" ht="28.5">
       <c r="A45" s="8">
         <v>8</v>
       </c>
@@ -2033,13 +2022,13 @@
         <v>44</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="27.6">
+    <row r="46" spans="1:6" ht="28.5">
       <c r="A46" s="8">
         <v>8</v>
       </c>
@@ -2053,18 +2042,18 @@
         <v>45</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="27.6">
+    <row r="47" spans="1:6" ht="28.5">
       <c r="A47" s="8">
         <v>8</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>90</v>
@@ -2073,18 +2062,18 @@
         <v>46</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="27.6">
+    <row r="48" spans="1:6" ht="28.5">
       <c r="A48" s="8">
         <v>8</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>90</v>
@@ -2093,13 +2082,13 @@
         <v>47</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="27.6">
+    <row r="49" spans="1:6" ht="28.5">
       <c r="A49" s="8">
         <v>9</v>
       </c>
@@ -2113,13 +2102,13 @@
         <v>48</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="27.6">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="28.5">
       <c r="A50" s="8">
         <v>10</v>
       </c>
@@ -2133,13 +2122,13 @@
         <v>49</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="27.6">
+    <row r="51" spans="1:6" ht="28.5">
       <c r="A51" s="8">
         <v>11</v>
       </c>
@@ -2153,13 +2142,13 @@
         <v>50</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="27.6">
+    <row r="52" spans="1:6" ht="28.5">
       <c r="A52" s="8">
         <v>12</v>
       </c>
@@ -2173,13 +2162,13 @@
         <v>51</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="41.4">
+    <row r="53" spans="1:6" ht="42.75">
       <c r="A53" s="8">
         <v>13</v>
       </c>
@@ -2193,13 +2182,13 @@
         <v>52</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="41.4">
+    <row r="54" spans="1:6" ht="42.75">
       <c r="A54" s="8">
         <v>14</v>
       </c>
@@ -2213,13 +2202,13 @@
         <v>53</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="27.6">
+    <row r="55" spans="1:6" ht="28.5">
       <c r="A55" s="8">
         <v>14</v>
       </c>
@@ -2233,13 +2222,13 @@
         <v>54</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="27.6">
+    <row r="56" spans="1:6" ht="28.5">
       <c r="A56" s="8">
         <v>14</v>
       </c>
@@ -2253,13 +2242,13 @@
         <v>55</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="27.6">
+    <row r="57" spans="1:6" ht="28.5">
       <c r="A57" s="8">
         <v>14</v>
       </c>
@@ -2273,13 +2262,13 @@
         <v>56</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="27.6">
+    <row r="58" spans="1:6" ht="28.5">
       <c r="A58" s="8">
         <v>14</v>
       </c>
@@ -2293,13 +2282,13 @@
         <v>57</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="27.6">
+    <row r="59" spans="1:6" ht="28.5">
       <c r="A59" s="8">
         <v>14</v>
       </c>
@@ -2313,13 +2302,13 @@
         <v>58</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="41.4">
+    <row r="60" spans="1:6" ht="42.75">
       <c r="A60" s="8">
         <v>14</v>
       </c>
@@ -2333,13 +2322,13 @@
         <v>59</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="27.6">
+    <row r="61" spans="1:6" ht="28.5">
       <c r="A61" s="8">
         <v>14</v>
       </c>
@@ -2353,13 +2342,13 @@
         <v>60</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="27.6">
+    <row r="62" spans="1:6" ht="28.5">
       <c r="A62" s="8">
         <v>14</v>
       </c>
@@ -2373,18 +2362,18 @@
         <v>61</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="55.2">
+    <row r="63" spans="1:6" ht="57">
       <c r="A63" s="8">
         <v>14</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>28</v>
@@ -2393,18 +2382,18 @@
         <v>62</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="41.4">
+    <row r="64" spans="1:6" ht="42.75">
       <c r="A64" s="8">
         <v>14</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>28</v>
@@ -2413,18 +2402,18 @@
         <v>63</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="27.6">
+    <row r="65" spans="1:6" ht="28.5">
       <c r="A65" s="8">
         <v>14</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>28</v>
@@ -2433,18 +2422,18 @@
         <v>64</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="41.4">
+    <row r="66" spans="1:6" ht="42.75">
       <c r="A66" s="8">
         <v>14</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>28</v>
@@ -2453,18 +2442,18 @@
         <v>65</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="27.6">
+    <row r="67" spans="1:6" ht="28.5">
       <c r="A67" s="8">
         <v>14</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>28</v>
@@ -2473,18 +2462,18 @@
         <v>66</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="27.6">
+    <row r="68" spans="1:6" ht="28.5">
       <c r="A68" s="8">
         <v>14</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>28</v>
@@ -2493,18 +2482,18 @@
         <v>67</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="27.6">
+    <row r="69" spans="1:6" ht="28.5">
       <c r="A69" s="8">
         <v>14</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>28</v>
@@ -2513,18 +2502,18 @@
         <v>68</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="41.4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="42.75">
       <c r="A70" s="8">
         <v>14</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>28</v>
@@ -2533,13 +2522,13 @@
         <v>69</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="41.4">
+    <row r="71" spans="1:6" ht="42.75">
       <c r="A71" s="8">
         <v>15</v>
       </c>
@@ -2553,13 +2542,13 @@
         <v>70</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="27.6">
+    <row r="72" spans="1:6" ht="28.5">
       <c r="A72" s="8">
         <v>16</v>
       </c>
@@ -2573,7 +2562,7 @@
         <v>71</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>62</v>
@@ -2593,7 +2582,7 @@
         <v>72</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>48</v>
@@ -2613,13 +2602,13 @@
         <v>73</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="27.6">
+    <row r="75" spans="1:6" ht="28.5">
       <c r="A75" s="8">
         <v>16</v>
       </c>
@@ -2633,7 +2622,7 @@
         <v>74</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>52</v>
@@ -2653,13 +2642,13 @@
         <v>75</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="27.6">
+    <row r="77" spans="1:6" ht="28.5">
       <c r="A77" s="8">
         <v>16</v>
       </c>
@@ -2673,13 +2662,13 @@
         <v>76</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="27.6">
+    <row r="78" spans="1:6" ht="28.5">
       <c r="A78" s="8">
         <v>16</v>
       </c>
@@ -2693,13 +2682,13 @@
         <v>77</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="55.2">
+    <row r="79" spans="1:6" ht="57">
       <c r="A79" s="8">
         <v>16</v>
       </c>
@@ -2713,13 +2702,13 @@
         <v>78</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="41.4">
+    <row r="80" spans="1:6" ht="42.75">
       <c r="A80" s="8">
         <v>16</v>
       </c>
@@ -2733,18 +2722,18 @@
         <v>79</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="41.4">
+    <row r="81" spans="1:6" ht="42.75">
       <c r="A81" s="8">
         <v>16</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>13</v>
@@ -2753,18 +2742,18 @@
         <v>80</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="41.4">
+    <row r="82" spans="1:6" ht="42.75">
       <c r="A82" s="8">
         <v>16</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>13</v>
@@ -2773,13 +2762,13 @@
         <v>81</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="27.6">
+    <row r="83" spans="1:6" ht="42.75">
       <c r="A83" s="8">
         <v>17</v>
       </c>
@@ -2793,13 +2782,13 @@
         <v>82</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="27.6">
+    <row r="84" spans="1:6" ht="42.75">
       <c r="A84" s="8">
         <v>17</v>
       </c>
@@ -2813,7 +2802,7 @@
         <v>83</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>89</v>
@@ -2833,13 +2822,13 @@
         <v>84</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="27.6">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="28.5">
       <c r="A86" s="8">
         <v>17</v>
       </c>
@@ -2853,7 +2842,7 @@
         <v>85</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>88</v>
@@ -2873,13 +2862,13 @@
         <v>86</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="41.4">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="42.75">
       <c r="A88" s="8">
         <v>17</v>
       </c>
@@ -2893,13 +2882,13 @@
         <v>87</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="27.6">
+    <row r="89" spans="1:6" ht="28.5">
       <c r="A89" s="8">
         <v>17</v>
       </c>
@@ -2913,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="27.6">
+    <row r="90" spans="1:6" ht="28.5">
       <c r="A90" s="8">
         <v>17</v>
       </c>
@@ -2933,13 +2922,13 @@
         <v>89</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="41.4">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="42.75">
       <c r="A91" s="8">
         <v>17</v>
       </c>
@@ -2953,7 +2942,7 @@
         <v>90</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>23</v>
@@ -2964,7 +2953,7 @@
         <v>17</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>84</v>
@@ -2973,13 +2962,13 @@
         <v>91</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="27.6">
+    <row r="93" spans="1:6" ht="28.5">
       <c r="A93" s="8">
         <v>18</v>
       </c>
@@ -2993,7 +2982,7 @@
         <v>92</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>75</v>
@@ -3013,7 +3002,7 @@
         <v>93</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>68</v>
